--- a/BRBY.L.xlsx
+++ b/BRBY.L.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF5D258-1A4F-4889-9847-F448F8357700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{443B150C-D276-4D9C-9618-3E6B441FC100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{C3EE2D3B-35B1-4886-BA08-2254D8777D41}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{C3EE2D3B-35B1-4886-BA08-2254D8777D41}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="68">
   <si>
     <t>Burberry</t>
   </si>
@@ -237,7 +237,10 @@
     <t>H226</t>
   </si>
   <si>
-    <t>Q226</t>
+    <t>FY26</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -247,13 +250,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -324,28 +333,32 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -703,7 +716,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="2">
-        <v>11.96</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -711,10 +724,10 @@
         <v>4</v>
       </c>
       <c r="I3" s="4">
-        <v>360.4</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>66</v>
+        <v>358.3</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -726,7 +739,7 @@
       </c>
       <c r="I4" s="4">
         <f>+I2*I3</f>
-        <v>4310.384</v>
+        <v>3916.2190000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -737,10 +750,10 @@
         <v>6</v>
       </c>
       <c r="I5" s="4">
-        <v>452</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>66</v>
+        <v>671</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -748,11 +761,11 @@
         <v>7</v>
       </c>
       <c r="I6" s="4">
-        <f>517+28</f>
-        <v>545</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>66</v>
+        <f>57+511</f>
+        <v>568</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -761,7 +774,7 @@
       </c>
       <c r="I7" s="4">
         <f>+I4-I5+I6</f>
-        <v>4403.384</v>
+        <v>3813.2190000000001</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -847,6 +860,9 @@
       <c r="Q2" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="R2" s="15" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="3" spans="1:66" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -867,7 +883,10 @@
         <f>120+116</f>
         <v>236</v>
       </c>
-      <c r="J3" s="12"/>
+      <c r="J3" s="12">
+        <f>+R3</f>
+        <v>233</v>
+      </c>
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
       <c r="M3" s="12"/>
@@ -877,7 +896,10 @@
       <c r="Q3" s="12">
         <v>237</v>
       </c>
-      <c r="R3" s="12"/>
+      <c r="R3" s="12">
+        <f>122+111</f>
+        <v>233</v>
+      </c>
       <c r="S3" s="12"/>
       <c r="T3" s="12"/>
       <c r="U3" s="12"/>
@@ -945,7 +967,10 @@
       <c r="I4" s="12">
         <v>98</v>
       </c>
-      <c r="J4" s="12"/>
+      <c r="J4" s="12">
+        <f t="shared" ref="J4:J7" si="1">+R4</f>
+        <v>98</v>
+      </c>
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
       <c r="M4" s="12"/>
@@ -955,7 +980,9 @@
       <c r="Q4" s="12">
         <v>100</v>
       </c>
-      <c r="R4" s="12"/>
+      <c r="R4" s="12">
+        <v>98</v>
+      </c>
       <c r="S4" s="12"/>
       <c r="T4" s="12"/>
       <c r="U4" s="12"/>
@@ -1023,7 +1050,10 @@
       <c r="I5" s="12">
         <v>81</v>
       </c>
-      <c r="J5" s="12"/>
+      <c r="J5" s="12">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
       <c r="K5" s="12"/>
       <c r="L5" s="12"/>
       <c r="M5" s="12"/>
@@ -1033,7 +1063,9 @@
       <c r="Q5" s="12">
         <v>85</v>
       </c>
-      <c r="R5" s="12"/>
+      <c r="R5" s="12">
+        <v>79</v>
+      </c>
       <c r="S5" s="12"/>
       <c r="T5" s="12"/>
       <c r="U5" s="12"/>
@@ -1105,30 +1137,36 @@
         <f>+SUM(I3:I5)</f>
         <v>415</v>
       </c>
-      <c r="J6" s="13"/>
+      <c r="J6" s="13">
+        <f>+SUM(J3:J5)</f>
+        <v>410</v>
+      </c>
       <c r="K6" s="13"/>
       <c r="L6" s="13"/>
       <c r="M6" s="13">
-        <f t="shared" ref="M6:P6" si="1">+SUM(M3:M5)</f>
+        <f t="shared" ref="M6:P6" si="2">+SUM(M3:M5)</f>
         <v>0</v>
       </c>
       <c r="N6" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O6" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P6" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q6" s="13">
         <f>+SUM(Q3:Q5)</f>
         <v>422</v>
       </c>
-      <c r="R6" s="13"/>
+      <c r="R6" s="13">
+        <f>+SUM(R3:R5)</f>
+        <v>410</v>
+      </c>
       <c r="S6" s="13"/>
       <c r="T6" s="12"/>
       <c r="U6" s="12"/>
@@ -1196,7 +1234,10 @@
       <c r="I7" s="12">
         <v>31</v>
       </c>
-      <c r="J7" s="12"/>
+      <c r="J7" s="12">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
       <c r="K7" s="12"/>
       <c r="L7" s="12"/>
       <c r="M7" s="12"/>
@@ -1206,7 +1247,9 @@
       <c r="Q7" s="12">
         <v>33</v>
       </c>
-      <c r="R7" s="12"/>
+      <c r="R7" s="12">
+        <v>27</v>
+      </c>
       <c r="S7" s="12"/>
       <c r="T7" s="12"/>
       <c r="U7" s="12"/>
@@ -1332,20 +1375,23 @@
         <v>498</v>
       </c>
       <c r="F9" s="12">
-        <f t="shared" ref="F9:F12" si="2">+P9-E9</f>
+        <f t="shared" ref="F9:F12" si="3">+P9-E9</f>
         <v>557</v>
       </c>
       <c r="G9" s="12">
         <v>367</v>
       </c>
       <c r="H9" s="12">
-        <f t="shared" ref="H9:H12" si="3">+Q9-G9</f>
+        <f t="shared" ref="H9:H12" si="4">+Q9-G9</f>
         <v>574</v>
       </c>
       <c r="I9" s="12">
         <v>343</v>
       </c>
-      <c r="J9" s="12"/>
+      <c r="J9" s="16">
+        <f>+R9-I9</f>
+        <v>494</v>
+      </c>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
       <c r="M9" s="12"/>
@@ -1357,7 +1403,9 @@
       <c r="Q9" s="12">
         <v>941</v>
       </c>
-      <c r="R9" s="12"/>
+      <c r="R9" s="12">
+        <v>837</v>
+      </c>
       <c r="S9" s="12"/>
       <c r="T9" s="12"/>
       <c r="U9" s="12"/>
@@ -1417,20 +1465,23 @@
         <v>391</v>
       </c>
       <c r="F10" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>469</v>
       </c>
       <c r="G10" s="12">
         <v>313</v>
       </c>
       <c r="H10" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>405</v>
       </c>
       <c r="I10" s="12">
         <v>313</v>
       </c>
-      <c r="J10" s="12"/>
+      <c r="J10" s="16">
+        <f t="shared" ref="J10:J18" si="5">+R10-I10</f>
+        <v>415</v>
+      </c>
       <c r="K10" s="12"/>
       <c r="L10" s="12"/>
       <c r="M10" s="12"/>
@@ -1442,7 +1493,9 @@
       <c r="Q10" s="12">
         <v>718</v>
       </c>
-      <c r="R10" s="12"/>
+      <c r="R10" s="12">
+        <v>728</v>
+      </c>
       <c r="S10" s="12"/>
       <c r="T10" s="12"/>
       <c r="U10" s="12"/>
@@ -1502,20 +1555,23 @@
         <v>399</v>
       </c>
       <c r="F11" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>443</v>
       </c>
       <c r="G11" s="12">
         <v>324</v>
       </c>
       <c r="H11" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>408</v>
       </c>
       <c r="I11" s="12">
         <v>324</v>
       </c>
-      <c r="J11" s="12"/>
+      <c r="J11" s="16">
+        <f t="shared" si="5"/>
+        <v>377</v>
+      </c>
       <c r="K11" s="12"/>
       <c r="L11" s="12"/>
       <c r="M11" s="12"/>
@@ -1527,7 +1583,9 @@
       <c r="Q11" s="12">
         <v>732</v>
       </c>
-      <c r="R11" s="12"/>
+      <c r="R11" s="12">
+        <v>701</v>
+      </c>
       <c r="S11" s="12"/>
       <c r="T11" s="12"/>
       <c r="U11" s="12"/>
@@ -1587,20 +1645,23 @@
         <v>77</v>
       </c>
       <c r="F12" s="12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
       <c r="G12" s="12">
         <v>50</v>
       </c>
       <c r="H12" s="12">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>54</v>
       </c>
       <c r="I12" s="12">
         <v>50</v>
       </c>
-      <c r="J12" s="12"/>
+      <c r="J12" s="16">
+        <f t="shared" si="5"/>
+        <v>43</v>
+      </c>
       <c r="K12" s="12"/>
       <c r="L12" s="12"/>
       <c r="M12" s="12"/>
@@ -1612,7 +1673,9 @@
       <c r="Q12" s="12">
         <v>104</v>
       </c>
-      <c r="R12" s="12"/>
+      <c r="R12" s="12">
+        <v>93</v>
+      </c>
       <c r="S12" s="12"/>
       <c r="T12" s="12"/>
       <c r="U12" s="12"/>
@@ -1686,7 +1749,10 @@
         <f>152+253</f>
         <v>405</v>
       </c>
-      <c r="J13" s="12"/>
+      <c r="J13" s="16">
+        <f t="shared" si="5"/>
+        <v>628</v>
+      </c>
       <c r="K13" s="12"/>
       <c r="L13" s="12"/>
       <c r="M13" s="12"/>
@@ -1698,7 +1764,10 @@
       <c r="Q13" s="12">
         <v>1043</v>
       </c>
-      <c r="R13" s="12"/>
+      <c r="R13" s="12">
+        <f>670+363</f>
+        <v>1033</v>
+      </c>
       <c r="S13" s="12"/>
       <c r="T13" s="12"/>
       <c r="U13" s="12"/>
@@ -1758,20 +1827,23 @@
         <v>485</v>
       </c>
       <c r="F14" s="12">
-        <f t="shared" ref="F14:F30" si="4">+P14-E14</f>
+        <f t="shared" ref="F14:F30" si="6">+P14-E14</f>
         <v>532</v>
       </c>
       <c r="G14" s="12">
         <v>392</v>
       </c>
       <c r="H14" s="12">
-        <f t="shared" ref="H14:H30" si="5">+Q14-G14</f>
+        <f t="shared" ref="H14:H30" si="7">+Q14-G14</f>
         <v>450</v>
       </c>
       <c r="I14" s="12">
         <v>381</v>
       </c>
-      <c r="J14" s="12"/>
+      <c r="J14" s="16">
+        <f t="shared" si="5"/>
+        <v>440</v>
+      </c>
       <c r="K14" s="12"/>
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
@@ -1783,7 +1855,9 @@
       <c r="Q14" s="12">
         <v>842</v>
       </c>
-      <c r="R14" s="12"/>
+      <c r="R14" s="12">
+        <v>821</v>
+      </c>
       <c r="S14" s="12"/>
       <c r="T14" s="12"/>
       <c r="U14" s="12"/>
@@ -1843,20 +1917,23 @@
         <v>296</v>
       </c>
       <c r="F15" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>307</v>
       </c>
       <c r="G15" s="12">
         <v>218</v>
       </c>
       <c r="H15" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>292</v>
       </c>
       <c r="I15" s="12">
         <v>216</v>
       </c>
-      <c r="J15" s="12"/>
+      <c r="J15" s="16">
+        <f t="shared" si="5"/>
+        <v>289</v>
+      </c>
       <c r="K15" s="12"/>
       <c r="L15" s="12"/>
       <c r="M15" s="12"/>
@@ -1868,7 +1945,9 @@
       <c r="Q15" s="12">
         <v>510</v>
       </c>
-      <c r="R15" s="12"/>
+      <c r="R15" s="12">
+        <v>505</v>
+      </c>
       <c r="S15" s="12"/>
       <c r="T15" s="12"/>
       <c r="U15" s="12"/>
@@ -1928,20 +2007,23 @@
         <v>1124</v>
       </c>
       <c r="F16" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1276</v>
       </c>
       <c r="G16" s="12">
         <v>885</v>
       </c>
       <c r="H16" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1191</v>
       </c>
       <c r="I16" s="12">
         <v>854</v>
       </c>
-      <c r="J16" s="12"/>
+      <c r="J16" s="16">
+        <f t="shared" si="5"/>
+        <v>1202</v>
+      </c>
       <c r="K16" s="12"/>
       <c r="L16" s="12"/>
       <c r="M16" s="12"/>
@@ -1953,7 +2035,9 @@
       <c r="Q16" s="12">
         <v>2076</v>
       </c>
-      <c r="R16" s="12"/>
+      <c r="R16" s="12">
+        <v>2056</v>
+      </c>
       <c r="S16" s="12"/>
       <c r="T16" s="12"/>
       <c r="U16" s="12"/>
@@ -2013,20 +2097,23 @@
         <v>241</v>
       </c>
       <c r="F17" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>265</v>
       </c>
       <c r="G17" s="12">
         <v>169</v>
       </c>
       <c r="H17" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>150</v>
       </c>
       <c r="I17" s="12">
         <v>148</v>
       </c>
-      <c r="J17" s="12"/>
+      <c r="J17" s="16">
+        <f t="shared" si="5"/>
+        <v>155</v>
+      </c>
       <c r="K17" s="12"/>
       <c r="L17" s="12"/>
       <c r="M17" s="12"/>
@@ -2038,7 +2125,9 @@
       <c r="Q17" s="12">
         <v>319</v>
       </c>
-      <c r="R17" s="12"/>
+      <c r="R17" s="12">
+        <v>303</v>
+      </c>
       <c r="S17" s="12"/>
       <c r="T17" s="12"/>
       <c r="U17" s="12"/>
@@ -2098,20 +2187,23 @@
         <v>31</v>
       </c>
       <c r="F18" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>31</v>
       </c>
       <c r="G18" s="12">
         <v>32</v>
       </c>
       <c r="H18" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>34</v>
       </c>
       <c r="I18" s="14">
         <v>30</v>
       </c>
-      <c r="J18" s="12"/>
+      <c r="J18" s="16">
+        <f t="shared" si="5"/>
+        <v>31</v>
+      </c>
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
       <c r="M18" s="12"/>
@@ -2123,7 +2215,9 @@
       <c r="Q18" s="12">
         <v>66</v>
       </c>
-      <c r="R18" s="12"/>
+      <c r="R18" s="12">
+        <v>61</v>
+      </c>
       <c r="S18" s="12"/>
       <c r="T18" s="12"/>
       <c r="U18" s="12"/>
@@ -2182,29 +2276,32 @@
         <v>0</v>
       </c>
       <c r="D19" s="13">
-        <f t="shared" ref="D19:H19" si="6">+SUM(D16:D18)</f>
+        <f t="shared" ref="D19:H19" si="8">+SUM(D16:D18)</f>
         <v>0</v>
       </c>
       <c r="E19" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1396</v>
       </c>
       <c r="F19" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1572</v>
       </c>
       <c r="G19" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1086</v>
       </c>
       <c r="H19" s="13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1375</v>
       </c>
       <c r="I19" s="13">
         <v>1032</v>
       </c>
-      <c r="J19" s="13"/>
+      <c r="J19" s="13">
+        <f>+R19-I19</f>
+        <v>1388</v>
+      </c>
       <c r="K19" s="12"/>
       <c r="L19" s="12"/>
       <c r="M19" s="12"/>
@@ -2216,7 +2313,9 @@
       <c r="Q19" s="13">
         <v>2461</v>
       </c>
-      <c r="R19" s="12"/>
+      <c r="R19" s="13">
+        <v>2420</v>
+      </c>
       <c r="S19" s="12"/>
       <c r="T19" s="12"/>
       <c r="U19" s="12"/>
@@ -2276,20 +2375,23 @@
         <v>421</v>
       </c>
       <c r="F20" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>538</v>
       </c>
       <c r="G20" s="12">
         <v>397</v>
       </c>
       <c r="H20" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>526</v>
       </c>
       <c r="I20" s="12">
         <v>331</v>
       </c>
-      <c r="J20" s="12"/>
+      <c r="J20" s="16">
+        <f>+R20-I20</f>
+        <v>446</v>
+      </c>
       <c r="K20" s="12"/>
       <c r="L20" s="12"/>
       <c r="M20" s="12"/>
@@ -2301,7 +2403,9 @@
       <c r="Q20" s="12">
         <v>923</v>
       </c>
-      <c r="R20" s="12"/>
+      <c r="R20" s="12">
+        <v>777</v>
+      </c>
       <c r="S20" s="12"/>
       <c r="T20" s="12"/>
       <c r="U20" s="12"/>
@@ -2356,19 +2460,19 @@
         <v>25</v>
       </c>
       <c r="C21" s="12">
-        <f t="shared" ref="C21:F21" si="7">+C19-C20</f>
+        <f t="shared" ref="C21:F21" si="9">+C19-C20</f>
         <v>0</v>
       </c>
       <c r="D21" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E21" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>975</v>
       </c>
       <c r="F21" s="12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1034</v>
       </c>
       <c r="G21" s="12">
@@ -2376,14 +2480,17 @@
         <v>689</v>
       </c>
       <c r="H21" s="12">
-        <f t="shared" ref="H21:I21" si="8">+H19-H20</f>
+        <f t="shared" ref="H21:J21" si="10">+H19-H20</f>
         <v>849</v>
       </c>
       <c r="I21" s="12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>701</v>
       </c>
-      <c r="J21" s="12"/>
+      <c r="J21" s="12">
+        <f t="shared" si="10"/>
+        <v>942</v>
+      </c>
       <c r="K21" s="12"/>
       <c r="L21" s="12"/>
       <c r="M21" s="12"/>
@@ -2397,7 +2504,10 @@
         <f>+Q19-Q20</f>
         <v>1538</v>
       </c>
-      <c r="R21" s="12"/>
+      <c r="R21" s="12">
+        <f>+R19-R20</f>
+        <v>1643</v>
+      </c>
       <c r="S21" s="12"/>
       <c r="T21" s="12"/>
       <c r="U21" s="12"/>
@@ -2457,20 +2567,23 @@
         <v>758</v>
       </c>
       <c r="F22" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>846</v>
       </c>
       <c r="G22" s="12">
         <v>755</v>
       </c>
       <c r="H22" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>757</v>
       </c>
       <c r="I22" s="12">
         <v>724</v>
       </c>
-      <c r="J22" s="12"/>
+      <c r="J22" s="16">
+        <f>+R22-I22</f>
+        <v>815</v>
+      </c>
       <c r="K22" s="12"/>
       <c r="L22" s="12"/>
       <c r="M22" s="12"/>
@@ -2482,7 +2595,9 @@
       <c r="Q22" s="12">
         <v>1512</v>
       </c>
-      <c r="R22" s="12"/>
+      <c r="R22" s="12">
+        <v>1539</v>
+      </c>
       <c r="S22" s="12"/>
       <c r="T22" s="12"/>
       <c r="U22" s="12"/>
@@ -2542,20 +2657,23 @@
         <v>6</v>
       </c>
       <c r="F23" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="G23" s="12">
         <v>13</v>
       </c>
       <c r="H23" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-42</v>
       </c>
       <c r="I23" s="12">
         <v>5</v>
       </c>
-      <c r="J23" s="12"/>
+      <c r="J23" s="16">
+        <f>+R23-I23</f>
+        <v>6</v>
+      </c>
       <c r="K23" s="12"/>
       <c r="L23" s="12"/>
       <c r="M23" s="12"/>
@@ -2567,7 +2685,9 @@
       <c r="Q23" s="12">
         <v>-29</v>
       </c>
-      <c r="R23" s="12"/>
+      <c r="R23" s="12">
+        <v>11</v>
+      </c>
       <c r="S23" s="12"/>
       <c r="T23" s="12"/>
       <c r="U23" s="12"/>
@@ -2622,19 +2742,19 @@
         <v>28</v>
       </c>
       <c r="C24" s="12">
-        <f t="shared" ref="C24:F24" si="9">+C21-C22+C23</f>
+        <f t="shared" ref="C24:F24" si="11">+C21-C22+C23</f>
         <v>0</v>
       </c>
       <c r="D24" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E24" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>223</v>
       </c>
       <c r="F24" s="12">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>195</v>
       </c>
       <c r="G24" s="12">
@@ -2642,40 +2762,46 @@
         <v>-53</v>
       </c>
       <c r="H24" s="12">
-        <f t="shared" ref="H24:Q24" si="10">+H21-H22+H23</f>
+        <f t="shared" ref="H24:R24" si="12">+H21-H22+H23</f>
         <v>50</v>
       </c>
       <c r="I24" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-18</v>
       </c>
-      <c r="J24" s="12"/>
+      <c r="J24" s="12">
+        <f t="shared" si="12"/>
+        <v>133</v>
+      </c>
       <c r="K24" s="12"/>
       <c r="L24" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M24" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N24" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="O24" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="P24" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>418</v>
       </c>
       <c r="Q24" s="12">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>-3</v>
       </c>
-      <c r="R24" s="12"/>
+      <c r="R24" s="12">
+        <f t="shared" si="12"/>
+        <v>115</v>
+      </c>
       <c r="S24" s="12"/>
       <c r="T24" s="12"/>
       <c r="U24" s="12"/>
@@ -2735,20 +2861,23 @@
         <v>20</v>
       </c>
       <c r="F25" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="G25" s="12">
         <v>11</v>
       </c>
       <c r="H25" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="I25" s="12">
         <v>14</v>
       </c>
-      <c r="J25" s="12"/>
+      <c r="J25" s="16">
+        <f>+R25-I25</f>
+        <v>9</v>
+      </c>
       <c r="K25" s="12"/>
       <c r="L25" s="12"/>
       <c r="M25" s="12"/>
@@ -2760,7 +2889,9 @@
       <c r="Q25" s="12">
         <v>25</v>
       </c>
-      <c r="R25" s="12"/>
+      <c r="R25" s="12">
+        <v>23</v>
+      </c>
       <c r="S25" s="12"/>
       <c r="T25" s="12"/>
       <c r="U25" s="12"/>
@@ -2820,20 +2951,23 @@
         <v>24</v>
       </c>
       <c r="F26" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>42</v>
       </c>
       <c r="G26" s="12">
         <v>38</v>
       </c>
       <c r="H26" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>50</v>
       </c>
       <c r="I26" s="12">
         <v>44</v>
       </c>
-      <c r="J26" s="12"/>
+      <c r="J26" s="16">
+        <f>+R26-I26</f>
+        <v>45</v>
+      </c>
       <c r="K26" s="12"/>
       <c r="L26" s="12"/>
       <c r="M26" s="12"/>
@@ -2845,7 +2979,9 @@
       <c r="Q26" s="12">
         <v>88</v>
       </c>
-      <c r="R26" s="12"/>
+      <c r="R26" s="12">
+        <v>89</v>
+      </c>
       <c r="S26" s="12"/>
       <c r="T26" s="12"/>
       <c r="U26" s="12"/>
@@ -2900,19 +3036,19 @@
         <v>31</v>
       </c>
       <c r="C27" s="12">
-        <f t="shared" ref="C27:F27" si="11">+C24+C25-C26</f>
+        <f t="shared" ref="C27:F27" si="13">+C24+C25-C26</f>
         <v>0</v>
       </c>
       <c r="D27" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="E27" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>219</v>
       </c>
       <c r="F27" s="12">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>164</v>
       </c>
       <c r="G27" s="12">
@@ -2927,33 +3063,39 @@
         <f>+I24+I25-I26</f>
         <v>-48</v>
       </c>
-      <c r="J27" s="12"/>
+      <c r="J27" s="12">
+        <f>+J24+J25-J26</f>
+        <v>97</v>
+      </c>
       <c r="K27" s="12"/>
       <c r="L27" s="12">
-        <f t="shared" ref="L27:Q27" si="12">+L24+L25-L26</f>
+        <f t="shared" ref="L27:R27" si="14">+L24+L25-L26</f>
         <v>0</v>
       </c>
       <c r="M27" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="N27" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="O27" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P27" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>383</v>
       </c>
       <c r="Q27" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>-66</v>
       </c>
-      <c r="R27" s="12"/>
+      <c r="R27" s="12">
+        <f t="shared" si="14"/>
+        <v>49</v>
+      </c>
       <c r="S27" s="12"/>
       <c r="T27" s="12"/>
       <c r="U27" s="12"/>
@@ -3013,20 +3155,23 @@
         <v>60</v>
       </c>
       <c r="F28" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>52</v>
       </c>
       <c r="G28" s="12">
         <v>-6</v>
       </c>
       <c r="H28" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="I28" s="12">
         <v>-21</v>
       </c>
-      <c r="J28" s="12"/>
+      <c r="J28" s="16">
+        <f>+R28-I28</f>
+        <v>50</v>
+      </c>
       <c r="K28" s="12"/>
       <c r="L28" s="12"/>
       <c r="M28" s="12"/>
@@ -3038,7 +3183,9 @@
       <c r="Q28" s="12">
         <v>9</v>
       </c>
-      <c r="R28" s="12"/>
+      <c r="R28" s="12">
+        <v>29</v>
+      </c>
       <c r="S28" s="12"/>
       <c r="T28" s="12"/>
       <c r="U28" s="12"/>
@@ -3093,19 +3240,19 @@
         <v>33</v>
       </c>
       <c r="C29" s="12">
-        <f t="shared" ref="C29:F29" si="13">+C27-C28</f>
+        <f t="shared" ref="C29:F29" si="15">+C27-C28</f>
         <v>0</v>
       </c>
       <c r="D29" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E29" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>159</v>
       </c>
       <c r="F29" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>112</v>
       </c>
       <c r="G29" s="12">
@@ -3113,40 +3260,46 @@
         <v>-74</v>
       </c>
       <c r="H29" s="12">
-        <f t="shared" ref="H29:Q29" si="14">+H27-H28</f>
+        <f t="shared" ref="H29:R29" si="16">+H27-H28</f>
         <v>-1</v>
       </c>
       <c r="I29" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-27</v>
       </c>
-      <c r="J29" s="12"/>
+      <c r="J29" s="12">
+        <f t="shared" si="16"/>
+        <v>47</v>
+      </c>
       <c r="K29" s="12"/>
       <c r="L29" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="M29" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="N29" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="O29" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="P29" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>271</v>
       </c>
       <c r="Q29" s="12">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>-75</v>
       </c>
-      <c r="R29" s="12"/>
+      <c r="R29" s="12">
+        <f t="shared" si="16"/>
+        <v>20</v>
+      </c>
       <c r="S29" s="12"/>
       <c r="T29" s="12"/>
       <c r="U29" s="12"/>
@@ -3206,20 +3359,23 @@
         <v>1</v>
       </c>
       <c r="F30" s="12">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G30" s="12">
         <v>0</v>
       </c>
       <c r="H30" s="12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I30" s="12">
         <v>-1</v>
       </c>
-      <c r="J30" s="12"/>
+      <c r="J30" s="16">
+        <f>+R30-I30</f>
+        <v>0</v>
+      </c>
       <c r="K30" s="12"/>
       <c r="L30" s="12"/>
       <c r="M30" s="12"/>
@@ -3231,7 +3387,9 @@
       <c r="Q30" s="12">
         <v>0</v>
       </c>
-      <c r="R30" s="12"/>
+      <c r="R30" s="12">
+        <v>-1</v>
+      </c>
       <c r="S30" s="12"/>
       <c r="T30" s="12"/>
       <c r="U30" s="12"/>
@@ -3286,11 +3444,11 @@
         <v>36</v>
       </c>
       <c r="C31" s="12">
-        <f t="shared" ref="C31:D31" si="15">+C29-C30</f>
+        <f t="shared" ref="C31:D31" si="17">+C29-C30</f>
         <v>0</v>
       </c>
       <c r="D31" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="E31" s="12">
@@ -3298,48 +3456,54 @@
         <v>158</v>
       </c>
       <c r="F31" s="12">
-        <f t="shared" ref="F31:Q31" si="16">+F29-F30</f>
+        <f t="shared" ref="F31:R31" si="18">+F29-F30</f>
         <v>112</v>
       </c>
       <c r="G31" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-74</v>
       </c>
       <c r="H31" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-1</v>
       </c>
       <c r="I31" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-26</v>
       </c>
-      <c r="J31" s="12"/>
+      <c r="J31" s="12">
+        <f t="shared" si="18"/>
+        <v>47</v>
+      </c>
       <c r="K31" s="12"/>
       <c r="L31" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M31" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N31" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="O31" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="P31" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>270</v>
       </c>
       <c r="Q31" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>-75</v>
       </c>
-      <c r="R31" s="12"/>
+      <c r="R31" s="12">
+        <f t="shared" si="18"/>
+        <v>21</v>
+      </c>
       <c r="S31" s="12"/>
       <c r="T31" s="12"/>
       <c r="U31" s="12"/>
@@ -3460,11 +3624,11 @@
         <v>34</v>
       </c>
       <c r="C33" s="7" t="e">
-        <f t="shared" ref="C33:D33" si="17">+C31/C34</f>
+        <f t="shared" ref="C33:D33" si="19">+C31/C34</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D33" s="7" t="e">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E33" s="7">
@@ -3472,45 +3636,51 @@
         <v>0.42347896006432589</v>
       </c>
       <c r="F33" s="7">
-        <f t="shared" ref="F33:I33" si="18">+F31/F34</f>
+        <f t="shared" ref="F33:J33" si="20">+F31/F34</f>
         <v>0.30584380120152921</v>
       </c>
       <c r="G33" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-0.20710887209627762</v>
       </c>
       <c r="H33" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-2.7901785714285715E-3</v>
       </c>
       <c r="I33" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>-7.2142064372918979E-2</v>
       </c>
-      <c r="J33" s="7"/>
+      <c r="J33" s="7">
+        <f t="shared" si="20"/>
+        <v>0.13117499302260674</v>
+      </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="7" t="e">
-        <f t="shared" ref="M33:P33" si="19">+M31/M34</f>
+        <f t="shared" ref="M33:P33" si="21">+M31/M34</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N33" s="7" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O33" s="7" t="e">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P33" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>0.73730202075368656</v>
       </c>
       <c r="Q33" s="7">
         <f>+Q31/Q34</f>
         <v>-0.20926339285714288</v>
       </c>
-      <c r="R33" s="4"/>
+      <c r="R33" s="7">
+        <f>+R31/R34</f>
+        <v>5.8610103265420037E-2</v>
+      </c>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
@@ -3583,7 +3753,9 @@
       <c r="I34" s="4">
         <v>360.4</v>
       </c>
-      <c r="J34" s="4"/>
+      <c r="J34" s="4">
+        <v>358.3</v>
+      </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
@@ -3595,7 +3767,9 @@
       <c r="Q34" s="4">
         <v>358.4</v>
       </c>
-      <c r="R34" s="4"/>
+      <c r="R34" s="4">
+        <v>358.3</v>
+      </c>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
@@ -3718,15 +3892,15 @@
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
       <c r="E36" s="8" t="e">
-        <f t="shared" ref="E36:G36" si="20">+E6/C6-1</f>
+        <f t="shared" ref="E36:G36" si="22">+E6/C6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F36" s="8" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G36" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1.6587677725118377E-2</v>
       </c>
       <c r="H36" s="8" t="e">
@@ -3741,19 +3915,19 @@
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
       <c r="M36" s="4" t="e">
-        <f t="shared" ref="M36:P36" si="21">+M6/L6-1</f>
+        <f t="shared" ref="M36:P36" si="23">+M6/L6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N36" s="4" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O36" s="4" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P36" s="4" t="e">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q36" s="4" t="e">
@@ -3817,15 +3991,15 @@
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="8" t="e">
-        <f t="shared" ref="E37:G39" si="22">+E13/C13-1</f>
+        <f t="shared" ref="E37:G39" si="24">+E13/C13-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F37" s="8" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G37" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-0.23972602739726023</v>
       </c>
       <c r="H37" s="8">
@@ -3840,23 +4014,23 @@
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="8" t="e">
-        <f t="shared" ref="M37:P38" si="23">+M13/L13-1</f>
+        <f t="shared" ref="M37:P38" si="25">+M13/L13-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N37" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O37" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P37" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q37" s="8">
-        <f t="shared" ref="Q37:Q38" si="24">+Q13/P13-1</f>
+        <f t="shared" ref="Q37:Q38" si="26">+Q13/P13-1</f>
         <v>-0.18895800933125972</v>
       </c>
       <c r="R37" s="4"/>
@@ -3916,46 +4090,46 @@
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="8" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F38" s="8" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G38" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-0.19175257731958761</v>
       </c>
       <c r="H38" s="8">
-        <f t="shared" ref="H38:I39" si="25">+H14/F14-1</f>
+        <f t="shared" ref="H38:I39" si="27">+H14/F14-1</f>
         <v>-0.15413533834586468</v>
       </c>
       <c r="I38" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-2.8061224489795866E-2</v>
       </c>
       <c r="J38" s="8"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
       <c r="M38" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N38" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O38" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P38" s="8" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q38" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>-0.17207472959685344</v>
       </c>
       <c r="R38" s="4"/>
@@ -4015,42 +4189,42 @@
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="8" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F39" s="8" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G39" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>-0.26351351351351349</v>
       </c>
       <c r="H39" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-4.8859934853420217E-2</v>
       </c>
       <c r="I39" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>-9.1743119266054496E-3</v>
       </c>
       <c r="J39" s="8"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
       <c r="M39" s="8" t="e">
-        <f t="shared" ref="M39:P39" si="26">+M15/L15-1</f>
+        <f t="shared" ref="M39:P39" si="28">+M15/L15-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N39" s="8" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O39" s="8" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P39" s="8" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q39" s="8">
@@ -4114,15 +4288,15 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
       <c r="E40" s="9" t="e">
-        <f t="shared" ref="E40:G40" si="27">+E19/C19-1</f>
+        <f t="shared" ref="E40:G40" si="29">+E19/C19-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F40" s="9" t="e">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G40" s="9">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-0.22206303724928367</v>
       </c>
       <c r="H40" s="9">
@@ -4137,19 +4311,19 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
       <c r="M40" s="9" t="e">
-        <f t="shared" ref="M40:P40" si="28">+M19/L19-1</f>
+        <f t="shared" ref="M40:P40" si="30">+M19/L19-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="N40" s="9" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O40" s="9" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P40" s="9" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="Q40" s="9">
@@ -4211,23 +4385,23 @@
         <v>59</v>
       </c>
       <c r="C41" s="8" t="e">
-        <f t="shared" ref="C41:G41" si="29">+C21/C19</f>
+        <f t="shared" ref="C41:G41" si="31">+C21/C19</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D41" s="8" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E41" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.6984240687679083</v>
       </c>
       <c r="F41" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.65776081424936383</v>
       </c>
       <c r="G41" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.63443830570902393</v>
       </c>
       <c r="H41" s="8">
@@ -4241,27 +4415,27 @@
       <c r="J41" s="8"/>
       <c r="K41" s="4"/>
       <c r="L41" s="8" t="e">
-        <f t="shared" ref="L41:Q41" si="30">+L21/L19</f>
+        <f t="shared" ref="L41:Q41" si="32">+L21/L19</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M41" s="8" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N41" s="8" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O41" s="8" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P41" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.67688679245283023</v>
       </c>
       <c r="Q41" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.62494920763917106</v>
       </c>
       <c r="R41" s="4"/>
@@ -4319,23 +4493,23 @@
         <v>60</v>
       </c>
       <c r="C42" s="8" t="e">
-        <f t="shared" ref="C42:G42" si="31">+C24/C19</f>
+        <f t="shared" ref="C42:G42" si="33">+C24/C19</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D42" s="8" t="e">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E42" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.15974212034383956</v>
       </c>
       <c r="F42" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.12404580152671756</v>
       </c>
       <c r="G42" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>-4.8802946593001842E-2</v>
       </c>
       <c r="H42" s="8">
@@ -4349,27 +4523,27 @@
       <c r="J42" s="8"/>
       <c r="K42" s="4"/>
       <c r="L42" s="8" t="e">
-        <f t="shared" ref="L42:Q42" si="32">+L24/L19</f>
+        <f t="shared" ref="L42:Q42" si="34">+L24/L19</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M42" s="8" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N42" s="8" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O42" s="8" t="e">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P42" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.14083557951482481</v>
       </c>
       <c r="Q42" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-1.2190166598943519E-3</v>
       </c>
       <c r="R42" s="4"/>
@@ -4427,23 +4601,23 @@
         <v>61</v>
       </c>
       <c r="C43" s="8" t="e">
-        <f t="shared" ref="C43:G43" si="33">+C28/C27</f>
+        <f t="shared" ref="C43:G43" si="35">+C28/C27</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D43" s="8" t="e">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E43" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.27397260273972601</v>
       </c>
       <c r="F43" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.31707317073170732</v>
       </c>
       <c r="G43" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="H43" s="8">
@@ -4457,27 +4631,27 @@
       <c r="J43" s="8"/>
       <c r="K43" s="4"/>
       <c r="L43" s="8" t="e">
-        <f t="shared" ref="L43:Q43" si="34">+L28/L27</f>
+        <f t="shared" ref="L43:Q43" si="36">+L28/L27</f>
         <v>#DIV/0!</v>
       </c>
       <c r="M43" s="8" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N43" s="8" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O43" s="8" t="e">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="P43" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>0.29242819843342038</v>
       </c>
       <c r="Q43" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="36"/>
         <v>-0.13636363636363635</v>
       </c>
       <c r="R43" s="4"/>
